--- a/diffusion-tn/validation/matrix_vs_tn_time_n=7.xlsx
+++ b/diffusion-tn/validation/matrix_vs_tn_time_n=7.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aditya/Desktop/UROPS/mps-fluid-dynamics/diffusion-tn/validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{65784EBB-AEA6-934A-AD7B-C6463B5D2395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C02032BC-4B1C-DF45-8AD4-2AA153D47C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="1" xr2:uid="{BE5BC5FD-85ED-6448-BA65-76B2FB435520}"/>
+    <workbookView xWindow="-27320" yWindow="-220" windowWidth="27320" windowHeight="19860" activeTab="1" xr2:uid="{BE5BC5FD-85ED-6448-BA65-76B2FB435520}"/>
   </bookViews>
   <sheets>
     <sheet name="matrix_vs_tn_time" sheetId="1" r:id="rId1"/>
-    <sheet name="setup" sheetId="3" r:id="rId2"/>
-    <sheet name="avg time per step" sheetId="4" r:id="rId3"/>
+    <sheet name="avg time per step" sheetId="4" r:id="rId2"/>
+    <sheet name="setup" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -816,1114 +816,6 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-GB" sz="1800"/>
-              <a:t>Setup time: Matrix vs TN time evolution</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>setup!$F$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Matrix (s)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>setup!$B$2:$B$5</c:f>
-              <c:numCache>
-                <c:formatCode>0</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>setup!$F$2:$F$5</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>9.5604200000000005E-4</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1.3242125E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.18037075</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8.551545291</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-F07A-8D4D-AFA6-FCB2CDFBCD0F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>setup!$E$1</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>TN=MPS+MPO (s)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>setup!$B$2:$B$5</c:f>
-              <c:numCache>
-                <c:formatCode>0</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>setup!$E$2:$E$5</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="4"/>
-                <c:pt idx="0">
-                  <c:v>1.1215875E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.4647415999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.1497583000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.23879283300000001</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-F07A-8D4D-AFA6-FCB2CDFBCD0F}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="411721151"/>
-        <c:axId val="404318271"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="411721151"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB" sz="1400"/>
-                  <a:t>System size, N</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="404318271"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="404318271"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB" sz="1400"/>
-                  <a:t>Setup</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-GB" sz="1400" baseline="0"/>
-                  <a:t> time (s)</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-GB" sz="1400"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="411721151"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1800"/>
-              <a:t>TN</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" sz="1800" baseline="0"/>
-              <a:t> Setup time vs System size N</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US" sz="1800"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="smoothMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>setup!$E$2:$E$8</c:f>
-              <c:strCache>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0.0112</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.0246</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.0715</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.2388</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.3218</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4.7740</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>21.5633</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>setup!$B$2:$B$8</c:f>
-              <c:numCache>
-                <c:formatCode>0</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>16</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>64</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>128</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>256</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>512</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1024</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>setup!$E$2:$E$8</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>1.1215875E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2.4647415999999998E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>7.1497583000000003E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.23879283300000001</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1.321781375</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4.774006</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>21.563312416999999</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-DA5E-5A4A-A67D-D023CBA0915C}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="380143807"/>
-        <c:axId val="375221183"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="380143807"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="1040"/>
-          <c:min val="0"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="5000"/>
-                  <a:lumOff val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB" sz="1400"/>
-                  <a:t>System size,</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-GB" sz="1400" baseline="0"/>
-                  <a:t> N</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-GB" sz="1400"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="375221183"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="375221183"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-GB" sz="1400"/>
-                  <a:t>TN Setup time</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-GB" sz="1400" baseline="0"/>
-                  <a:t> (s)</a:t>
-                </a:r>
-                <a:endParaRPr lang="en-GB" sz="1400"/>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="380143807"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-GB" sz="1800"/>
               <a:t>Average time per</a:t>
             </a:r>
             <a:r>
@@ -2483,7 +1375,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -2522,7 +1414,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-US" sz="1800" baseline="0"/>
-              <a:t> time per step: TN only</a:t>
+              <a:t> time per TN step vs N</a:t>
             </a:r>
             <a:endParaRPr lang="en-US" sz="1800"/>
           </a:p>
@@ -2859,7 +1751,15 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-GB" sz="1400"/>
-                  <a:t>Time taken per evolution step (s)</a:t>
+                  <a:t>Average</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1400" baseline="0"/>
+                  <a:t> t</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1400"/>
+                  <a:t>ime taken per step (s)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -2931,6 +1831,1114 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="395023167"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800"/>
+              <a:t>Setup time: Matrix vs TN time evolution</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>setup!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Matrix (s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>setup!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>setup!$F$2:$F$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>9.5604200000000005E-4</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1.3242125E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.18037075</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.551545291</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F07A-8D4D-AFA6-FCB2CDFBCD0F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>setup!$E$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TN=MPS+MPO (s)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>setup!$B$2:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>setup!$E$2:$E$5</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1.1215875E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.4647415999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.1497583000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.23879283300000001</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-F07A-8D4D-AFA6-FCB2CDFBCD0F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="411721151"/>
+        <c:axId val="404318271"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="411721151"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1400"/>
+                  <a:t>System size, N</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="404318271"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="404318271"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1400"/>
+                  <a:t>Setup</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1400" baseline="0"/>
+                  <a:t> time (s)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB" sz="1400"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="411721151"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800"/>
+              <a:t>TN</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800" baseline="0"/>
+              <a:t> Setup time vs System size N</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US" sz="1800"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="smoothMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>setup!$E$2:$E$8</c:f>
+              <c:strCache>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0.0112</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.0246</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.0715</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.2388</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.3218</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.7740</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21.5633</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>setup!$B$2:$B$8</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>128</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>256</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>512</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1024</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>setup!$E$2:$E$8</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>1.1215875E-2</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2.4647415999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7.1497583000000003E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.23879283300000001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.321781375</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4.774006</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>21.563312416999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-DA5E-5A4A-A67D-D023CBA0915C}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="380143807"/>
+        <c:axId val="375221183"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="380143807"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1040"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:minorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="5000"/>
+                  <a:lumOff val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:minorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1400"/>
+                  <a:t>System size,</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1400" baseline="0"/>
+                  <a:t> N</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB" sz="1400"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="375221183"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="375221183"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1400"/>
+                  <a:t>TN Setup time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-GB" sz="1400" baseline="0"/>
+                  <a:t> (s)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-GB" sz="1400"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="380143807"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -5214,6 +5222,83 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>786423</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>74735</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>392724</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>201736</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F1DE818-E829-7050-B3B2-A7770A00552A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>74733</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>435221</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>61058</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{363D72CE-72E5-2422-72CB-7DDE1C03D13A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>558800</xdr:colOff>
       <xdr:row>11</xdr:row>
@@ -5287,83 +5372,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>786423</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>74735</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>392724</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>201736</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F1DE818-E829-7050-B3B2-A7770A00552A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>74733</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>435221</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>61058</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{363D72CE-72E5-2422-72CB-7DDE1C03D13A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69DD871A-B658-3E4D-9134-2FA508086801}" name="Table1" displayName="Table1" ref="A1:I701" totalsRowShown="0" dataDxfId="20">
   <autoFilter ref="A1:I701" xr:uid="{69DD871A-B658-3E4D-9134-2FA508086801}"/>
@@ -5383,6 +5391,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{52CC4271-737A-7743-9E9C-14F013317013}" name="Table2" displayName="Table2" ref="A1:D8" totalsRowShown="0" dataDxfId="5">
+  <autoFilter ref="A1:D8" xr:uid="{52CC4271-737A-7743-9E9C-14F013317013}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{1318D5EC-682A-7D4A-8D44-E27AA37130DB}" name="n" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{1E076BEF-2430-0F4B-AE76-62F7135F06FE}" name="N=2^n" dataDxfId="0">
+      <calculatedColumnFormula>2^Table2[[#This Row],[n]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="2" xr3:uid="{3E32F3CF-8916-0D4B-9C49-A9ADB0FDAA5A}" name="Matrix" dataDxfId="3">
+      <calculatedColumnFormula array="1">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!E:E,matrix_vs_tn_time!A:A=A2))</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="3" xr3:uid="{DC66C0E1-8197-4240-B8D2-8C9AF1BB27B9}" name="TN" dataDxfId="2">
+      <calculatedColumnFormula array="1">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A2))</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D8044509-3D7D-D249-8217-3739FE4A9328}" name="Table3" displayName="Table3" ref="A1:F8" totalsRowShown="0">
   <autoFilter ref="A1:F8" xr:uid="{D8044509-3D7D-D249-8217-3739FE4A9328}"/>
   <tableColumns count="6">
@@ -5401,25 +5428,6 @@
     </tableColumn>
     <tableColumn id="2" xr3:uid="{957F1B12-B2CF-7342-B5E1-3676122282E0}" name="Matrix (s)" dataDxfId="6">
       <calculatedColumnFormula array="1">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!G:G,matrix_vs_tn_time!$A:$A=$A2))</calculatedColumnFormula>
-    </tableColumn>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{52CC4271-737A-7743-9E9C-14F013317013}" name="Table2" displayName="Table2" ref="A1:D8" totalsRowShown="0" dataDxfId="5">
-  <autoFilter ref="A1:D8" xr:uid="{52CC4271-737A-7743-9E9C-14F013317013}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{1318D5EC-682A-7D4A-8D44-E27AA37130DB}" name="n" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{1E076BEF-2430-0F4B-AE76-62F7135F06FE}" name="N=2^n" dataDxfId="0">
-      <calculatedColumnFormula>2^Table2[[#This Row],[n]]</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="2" xr3:uid="{3E32F3CF-8916-0D4B-9C49-A9ADB0FDAA5A}" name="Matrix" dataDxfId="3">
-      <calculatedColumnFormula array="1">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!E:E,matrix_vs_tn_time!A:A=A2))</calculatedColumnFormula>
-    </tableColumn>
-    <tableColumn id="3" xr3:uid="{DC66C0E1-8197-4240-B8D2-8C9AF1BB27B9}" name="TN" dataDxfId="2">
-      <calculatedColumnFormula array="1">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A2))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -26090,195 +26098,133 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{526D4C6D-9985-2D42-801C-BC368A30B46D}">
-  <dimension ref="A1:F8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8167EB36-A17F-1748-8F7B-882F2BBBEC52}">
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" t="s">
         <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="5">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="3">
         <v>4</v>
       </c>
-      <c r="B2" s="5">
-        <f>2^Table3[[#This Row],[n]]</f>
+      <c r="B2" s="3">
+        <f>2^Table2[[#This Row],[n]]</f>
         <v>16</v>
       </c>
-      <c r="C2" s="2" cm="1">
-        <f t="array" ref="C2">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!H:H,matrix_vs_tn_time!$A:$A=$A2))</f>
-        <v>2.5533750000000001E-3</v>
-      </c>
-      <c r="D2" s="2" cm="1">
-        <f t="array" ref="D2">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!I:I,matrix_vs_tn_time!$A:$A=$A2))</f>
-        <v>8.6625000000000001E-3</v>
-      </c>
-      <c r="E2" s="2">
-        <f>C2+D2</f>
-        <v>1.1215875E-2</v>
-      </c>
-      <c r="F2" s="2" cm="1">
-        <f t="array" ref="F2">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!G:G,matrix_vs_tn_time!$A:$A=$A2))</f>
-        <v>9.5604200000000005E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C2" s="4" cm="1">
+        <f t="array" ref="C2">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!E:E,matrix_vs_tn_time!A:A=A2))</f>
+        <v>1.4625E-5</v>
+      </c>
+      <c r="D2" s="4" cm="1">
+        <f t="array" ref="D2">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A2))</f>
+        <v>9.3631249999999997E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>5</v>
       </c>
       <c r="B3" s="3">
-        <f>2^Table3[[#This Row],[n]]</f>
+        <f>2^Table2[[#This Row],[n]]</f>
         <v>32</v>
       </c>
-      <c r="C3" s="2" cm="1">
-        <f t="array" ref="C3">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!H:H,matrix_vs_tn_time!$A:$A=$A3))</f>
-        <v>1.7262E-2</v>
-      </c>
-      <c r="D3" s="2" cm="1">
-        <f t="array" ref="D3">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!I:I,matrix_vs_tn_time!$A:$A=$A3))</f>
-        <v>7.3854159999999997E-3</v>
-      </c>
-      <c r="E3" s="2">
-        <f t="shared" ref="E3:E8" si="0">C3+D3</f>
-        <v>2.4647415999999998E-2</v>
-      </c>
-      <c r="F3" s="2" cm="1">
-        <f t="array" ref="F3">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!G:G,matrix_vs_tn_time!$A:$A=$A3))</f>
-        <v>1.3242125E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="5">
+      <c r="C3" s="4" cm="1">
+        <f t="array" ref="C3">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!E:E,matrix_vs_tn_time!A:A=A3))</f>
+        <v>4.3379200000000001E-4</v>
+      </c>
+      <c r="D3" s="4" cm="1">
+        <f t="array" ref="D3">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A3))</f>
+        <v>1.304354E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="3">
         <v>6</v>
       </c>
-      <c r="B4" s="5">
-        <f>2^Table3[[#This Row],[n]]</f>
+      <c r="B4" s="3">
+        <f>2^Table2[[#This Row],[n]]</f>
         <v>64</v>
       </c>
-      <c r="C4" s="2" cm="1">
-        <f t="array" ref="C4">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!H:H,matrix_vs_tn_time!$A:$A=$A4))</f>
-        <v>5.7753791999999998E-2</v>
-      </c>
-      <c r="D4" s="2" cm="1">
-        <f t="array" ref="D4">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!I:I,matrix_vs_tn_time!$A:$A=$A4))</f>
-        <v>1.3743791E-2</v>
-      </c>
-      <c r="E4" s="2">
-        <f t="shared" si="0"/>
-        <v>7.1497583000000003E-2</v>
-      </c>
-      <c r="F4" s="2" cm="1">
-        <f t="array" ref="F4">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!G:G,matrix_vs_tn_time!$A:$A=$A4))</f>
-        <v>0.18037075</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C4" s="4" cm="1">
+        <f t="array" ref="C4">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!E:E,matrix_vs_tn_time!A:A=A4))</f>
+        <v>3.4262914999999999E-3</v>
+      </c>
+      <c r="D4" s="4" cm="1">
+        <f t="array" ref="D4">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A4))</f>
+        <v>1.7920004999999999E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>7</v>
       </c>
       <c r="B5" s="3">
-        <f>2^Table3[[#This Row],[n]]</f>
+        <f>2^Table2[[#This Row],[n]]</f>
         <v>128</v>
       </c>
-      <c r="C5" s="2" cm="1">
-        <f t="array" ref="C5">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!H:H,matrix_vs_tn_time!$A:$A=$A5))</f>
-        <v>0.22817095800000001</v>
-      </c>
-      <c r="D5" s="2" cm="1">
-        <f t="array" ref="D5">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!I:I,matrix_vs_tn_time!$A:$A=$A5))</f>
-        <v>1.0621874999999999E-2</v>
-      </c>
-      <c r="E5" s="2">
-        <f t="shared" si="0"/>
-        <v>0.23879283300000001</v>
-      </c>
-      <c r="F5" s="2" cm="1">
-        <f t="array" ref="F5">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!G:G,matrix_vs_tn_time!$A:$A=$A5))</f>
-        <v>8.551545291</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A6" s="5">
+      <c r="C5" s="4" cm="1">
+        <f t="array" ref="C5">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!E:E,matrix_vs_tn_time!A:A=A5))</f>
+        <v>3.0302395499999999E-2</v>
+      </c>
+      <c r="D5" s="4" cm="1">
+        <f t="array" ref="D5">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A5))</f>
+        <v>2.5170625000000002E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
         <v>8</v>
       </c>
-      <c r="B6" s="5">
-        <f>2^Table3[[#This Row],[n]]</f>
+      <c r="B6" s="3">
+        <f>2^Table2[[#This Row],[n]]</f>
         <v>256</v>
       </c>
-      <c r="C6" s="2" cm="1">
-        <f t="array" ref="C6">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!H:H,matrix_vs_tn_time!$A:$A=$A6))</f>
-        <v>1.307838375</v>
-      </c>
-      <c r="D6" s="2" cm="1">
-        <f t="array" ref="D6">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!I:I,matrix_vs_tn_time!$A:$A=$A6))</f>
-        <v>1.3943000000000001E-2</v>
-      </c>
-      <c r="E6" s="2">
-        <f t="shared" si="0"/>
-        <v>1.321781375</v>
-      </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C6" s="4"/>
+      <c r="D6" s="4" cm="1">
+        <f t="array" ref="D6">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A6))</f>
+        <v>1.8052084999999999E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>9</v>
       </c>
       <c r="B7" s="3">
-        <f>2^Table3[[#This Row],[n]]</f>
+        <f>2^Table2[[#This Row],[n]]</f>
         <v>512</v>
       </c>
-      <c r="C7" s="2" cm="1">
-        <f t="array" ref="C7">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!H:H,matrix_vs_tn_time!$A:$A=$A7))</f>
-        <v>4.7618457080000001</v>
-      </c>
-      <c r="D7" s="2" cm="1">
-        <f t="array" ref="D7">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!I:I,matrix_vs_tn_time!$A:$A=$A7))</f>
-        <v>1.2160292E-2</v>
-      </c>
-      <c r="E7" s="2">
-        <f t="shared" si="0"/>
-        <v>4.774006</v>
-      </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="6">
+      <c r="C7" s="4"/>
+      <c r="D7" s="4" cm="1">
+        <f t="array" ref="D7">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A7))</f>
+        <v>2.0613329999999998E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
         <v>10</v>
       </c>
-      <c r="B8" s="8">
-        <f>2^Table3[[#This Row],[n]]</f>
+      <c r="B8" s="3">
+        <f>2^Table2[[#This Row],[n]]</f>
         <v>1024</v>
       </c>
-      <c r="C8" s="2" cm="1">
-        <f t="array" ref="C8">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!H:H,matrix_vs_tn_time!$A:$A=$A8))</f>
-        <v>21.546614916999999</v>
-      </c>
-      <c r="D8" s="2" cm="1">
-        <f t="array" ref="D8">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!I:I,matrix_vs_tn_time!$A:$A=$A8))</f>
-        <v>1.6697500000000001E-2</v>
-      </c>
-      <c r="E8" s="2">
-        <f t="shared" si="0"/>
-        <v>21.563312416999999</v>
-      </c>
-      <c r="F8" s="2"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4" cm="1">
+        <f t="array" ref="D8">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A8))</f>
+        <v>2.3729789999999999E-3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -26290,133 +26236,195 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8167EB36-A17F-1748-8F7B-882F2BBBEC52}">
-  <dimension ref="A1:D8"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{526D4C6D-9985-2D42-801C-BC368A30B46D}">
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="3">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="5">
         <v>4</v>
       </c>
-      <c r="B2" s="3">
-        <f>2^Table2[[#This Row],[n]]</f>
+      <c r="B2" s="5">
+        <f>2^Table3[[#This Row],[n]]</f>
         <v>16</v>
       </c>
-      <c r="C2" s="4" cm="1">
-        <f t="array" ref="C2">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!E:E,matrix_vs_tn_time!A:A=A2))</f>
-        <v>1.4625E-5</v>
-      </c>
-      <c r="D2" s="4" cm="1">
-        <f t="array" ref="D2">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A2))</f>
-        <v>9.3631249999999997E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C2" s="2" cm="1">
+        <f t="array" ref="C2">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!H:H,matrix_vs_tn_time!$A:$A=$A2))</f>
+        <v>2.5533750000000001E-3</v>
+      </c>
+      <c r="D2" s="2" cm="1">
+        <f t="array" ref="D2">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!I:I,matrix_vs_tn_time!$A:$A=$A2))</f>
+        <v>8.6625000000000001E-3</v>
+      </c>
+      <c r="E2" s="2">
+        <f>C2+D2</f>
+        <v>1.1215875E-2</v>
+      </c>
+      <c r="F2" s="2" cm="1">
+        <f t="array" ref="F2">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!G:G,matrix_vs_tn_time!$A:$A=$A2))</f>
+        <v>9.5604200000000005E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>5</v>
       </c>
       <c r="B3" s="3">
-        <f>2^Table2[[#This Row],[n]]</f>
+        <f>2^Table3[[#This Row],[n]]</f>
         <v>32</v>
       </c>
-      <c r="C3" s="4" cm="1">
-        <f t="array" ref="C3">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!E:E,matrix_vs_tn_time!A:A=A3))</f>
-        <v>4.3379200000000001E-4</v>
-      </c>
-      <c r="D3" s="4" cm="1">
-        <f t="array" ref="D3">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A3))</f>
-        <v>1.304354E-3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="3">
+      <c r="C3" s="2" cm="1">
+        <f t="array" ref="C3">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!H:H,matrix_vs_tn_time!$A:$A=$A3))</f>
+        <v>1.7262E-2</v>
+      </c>
+      <c r="D3" s="2" cm="1">
+        <f t="array" ref="D3">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!I:I,matrix_vs_tn_time!$A:$A=$A3))</f>
+        <v>7.3854159999999997E-3</v>
+      </c>
+      <c r="E3" s="2">
+        <f t="shared" ref="E3:E8" si="0">C3+D3</f>
+        <v>2.4647415999999998E-2</v>
+      </c>
+      <c r="F3" s="2" cm="1">
+        <f t="array" ref="F3">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!G:G,matrix_vs_tn_time!$A:$A=$A3))</f>
+        <v>1.3242125E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
         <v>6</v>
       </c>
-      <c r="B4" s="3">
-        <f>2^Table2[[#This Row],[n]]</f>
+      <c r="B4" s="5">
+        <f>2^Table3[[#This Row],[n]]</f>
         <v>64</v>
       </c>
-      <c r="C4" s="4" cm="1">
-        <f t="array" ref="C4">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!E:E,matrix_vs_tn_time!A:A=A4))</f>
-        <v>3.4262914999999999E-3</v>
-      </c>
-      <c r="D4" s="4" cm="1">
-        <f t="array" ref="D4">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A4))</f>
-        <v>1.7920004999999999E-3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C4" s="2" cm="1">
+        <f t="array" ref="C4">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!H:H,matrix_vs_tn_time!$A:$A=$A4))</f>
+        <v>5.7753791999999998E-2</v>
+      </c>
+      <c r="D4" s="2" cm="1">
+        <f t="array" ref="D4">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!I:I,matrix_vs_tn_time!$A:$A=$A4))</f>
+        <v>1.3743791E-2</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" si="0"/>
+        <v>7.1497583000000003E-2</v>
+      </c>
+      <c r="F4" s="2" cm="1">
+        <f t="array" ref="F4">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!G:G,matrix_vs_tn_time!$A:$A=$A4))</f>
+        <v>0.18037075</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>7</v>
       </c>
       <c r="B5" s="3">
-        <f>2^Table2[[#This Row],[n]]</f>
+        <f>2^Table3[[#This Row],[n]]</f>
         <v>128</v>
       </c>
-      <c r="C5" s="4" cm="1">
-        <f t="array" ref="C5">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!E:E,matrix_vs_tn_time!A:A=A5))</f>
-        <v>3.0302395499999999E-2</v>
-      </c>
-      <c r="D5" s="4" cm="1">
-        <f t="array" ref="D5">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A5))</f>
-        <v>2.5170625000000002E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="3">
+      <c r="C5" s="2" cm="1">
+        <f t="array" ref="C5">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!H:H,matrix_vs_tn_time!$A:$A=$A5))</f>
+        <v>0.22817095800000001</v>
+      </c>
+      <c r="D5" s="2" cm="1">
+        <f t="array" ref="D5">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!I:I,matrix_vs_tn_time!$A:$A=$A5))</f>
+        <v>1.0621874999999999E-2</v>
+      </c>
+      <c r="E5" s="2">
+        <f t="shared" si="0"/>
+        <v>0.23879283300000001</v>
+      </c>
+      <c r="F5" s="2" cm="1">
+        <f t="array" ref="F5">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!G:G,matrix_vs_tn_time!$A:$A=$A5))</f>
+        <v>8.551545291</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
         <v>8</v>
       </c>
-      <c r="B6" s="3">
-        <f>2^Table2[[#This Row],[n]]</f>
+      <c r="B6" s="5">
+        <f>2^Table3[[#This Row],[n]]</f>
         <v>256</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4" cm="1">
-        <f t="array" ref="D6">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A6))</f>
-        <v>1.8052084999999999E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="C6" s="2" cm="1">
+        <f t="array" ref="C6">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!H:H,matrix_vs_tn_time!$A:$A=$A6))</f>
+        <v>1.307838375</v>
+      </c>
+      <c r="D6" s="2" cm="1">
+        <f t="array" ref="D6">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!I:I,matrix_vs_tn_time!$A:$A=$A6))</f>
+        <v>1.3943000000000001E-2</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="0"/>
+        <v>1.321781375</v>
+      </c>
+      <c r="F6" s="2"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>9</v>
       </c>
       <c r="B7" s="3">
-        <f>2^Table2[[#This Row],[n]]</f>
+        <f>2^Table3[[#This Row],[n]]</f>
         <v>512</v>
       </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4" cm="1">
-        <f t="array" ref="D7">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A7))</f>
-        <v>2.0613329999999998E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
+      <c r="C7" s="2" cm="1">
+        <f t="array" ref="C7">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!H:H,matrix_vs_tn_time!$A:$A=$A7))</f>
+        <v>4.7618457080000001</v>
+      </c>
+      <c r="D7" s="2" cm="1">
+        <f t="array" ref="D7">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!I:I,matrix_vs_tn_time!$A:$A=$A7))</f>
+        <v>1.2160292E-2</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="0"/>
+        <v>4.774006</v>
+      </c>
+      <c r="F7" s="2"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="6">
         <v>10</v>
       </c>
-      <c r="B8" s="3">
-        <f>2^Table2[[#This Row],[n]]</f>
+      <c r="B8" s="8">
+        <f>2^Table3[[#This Row],[n]]</f>
         <v>1024</v>
       </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4" cm="1">
-        <f t="array" ref="D8">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A8))</f>
-        <v>2.3729789999999999E-3</v>
-      </c>
+      <c r="C8" s="2" cm="1">
+        <f t="array" ref="C8">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!H:H,matrix_vs_tn_time!$A:$A=$A8))</f>
+        <v>21.546614916999999</v>
+      </c>
+      <c r="D8" s="2" cm="1">
+        <f t="array" ref="D8">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!I:I,matrix_vs_tn_time!$A:$A=$A8))</f>
+        <v>1.6697500000000001E-2</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="0"/>
+        <v>21.563312416999999</v>
+      </c>
+      <c r="F8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/diffusion-tn/validation/matrix_vs_tn_time_n=7.xlsx
+++ b/diffusion-tn/validation/matrix_vs_tn_time_n=7.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aditya/Desktop/UROPS/mps-fluid-dynamics/diffusion-tn/validation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C02032BC-4B1C-DF45-8AD4-2AA153D47C69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38C506F-FC43-4340-ADF4-573B51F2F6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-27320" yWindow="-220" windowWidth="27320" windowHeight="19860" activeTab="1" xr2:uid="{BE5BC5FD-85ED-6448-BA65-76B2FB435520}"/>
   </bookViews>
   <sheets>
     <sheet name="matrix_vs_tn_time" sheetId="1" r:id="rId1"/>
-    <sheet name="avg time per step" sheetId="4" r:id="rId2"/>
+    <sheet name="median time per step" sheetId="4" r:id="rId2"/>
     <sheet name="setup" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -115,8 +115,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -621,16 +621,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="33" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -678,7 +677,16 @@
   </cellStyles>
   <dxfs count="21">
     <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
+      <numFmt numFmtId="164" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0000"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -688,30 +696,6 @@
           <bgColor theme="0" tint="-0.14999847407452621"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="169" formatCode="0.000000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.0000"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="0.0000"/>
     </dxf>
     <dxf>
       <font>
@@ -739,25 +723,40 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="0.0000"/>
+      <numFmt numFmtId="164" formatCode="0.0000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="0.0000"/>
+      <numFmt numFmtId="164" formatCode="0.0000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="0.0000"/>
+      <numFmt numFmtId="164" formatCode="0.0000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="0.000000"/>
+      <numFmt numFmtId="165" formatCode="0.000000"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="169" formatCode="0.000000"/>
+      <numFmt numFmtId="165" formatCode="0.000000"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.000000"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.000000"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
@@ -816,7 +815,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-GB" sz="1800"/>
-              <a:t>Average time per</a:t>
+              <a:t>Median time per</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-GB" sz="1800" baseline="0"/>
@@ -851,7 +850,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="en-GB"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -866,7 +865,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'avg time per step'!$C$1</c:f>
+              <c:f>'median time per step'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -901,7 +900,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'avg time per step'!$B$2:$B$5</c:f>
+              <c:f>'median time per step'!$B$2:$B$5</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="4"/>
@@ -922,7 +921,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'avg time per step'!$C$2:$C$5</c:f>
+              <c:f>'median time per step'!$C$2:$C$5</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="4"/>
@@ -953,7 +952,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'avg time per step'!$D$1</c:f>
+              <c:f>'median time per step'!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -988,7 +987,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'avg time per step'!$B$2:$B$5</c:f>
+              <c:f>'median time per step'!$B$2:$B$5</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1009,7 +1008,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'avg time per step'!$D$2:$D$5</c:f>
+              <c:f>'median time per step'!$D$2:$D$5</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="4"/>
@@ -1125,7 +1124,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-GB"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1212,11 +1211,11 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-GB" sz="1400"/>
-                  <a:t>Average</a:t>
+                  <a:t>Median</a:t>
                 </a:r>
                 <a:r>
                   <a:rPr lang="en-GB" sz="1400" baseline="0"/>
-                  <a:t> time taken per evolution step (S)</a:t>
+                  <a:t> time taken per step (s)</a:t>
                 </a:r>
                 <a:endParaRPr lang="en-GB" sz="1400"/>
               </a:p>
@@ -1247,7 +1246,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-GB"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1410,7 +1409,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US" sz="1800"/>
-              <a:t>Average</a:t>
+              <a:t>Median</a:t>
             </a:r>
             <a:r>
               <a:rPr lang="en-US" sz="1800" baseline="0"/>
@@ -1460,7 +1459,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'avg time per step'!$D$1</c:f>
+              <c:f>'median time per step'!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1495,7 +1494,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'avg time per step'!$B$2:$B$8</c:f>
+              <c:f>'median time per step'!$B$2:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1525,7 +1524,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'avg time per step'!$D$2:$D$8</c:f>
+              <c:f>'median time per step'!$D$2:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>0.000000</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1664,7 +1663,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-GB"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -1751,7 +1750,7 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr lang="en-GB" sz="1400"/>
-                  <a:t>Average</a:t>
+                  <a:t>Median</a:t>
                 </a:r>
                 <a:r>
                   <a:rPr lang="en-GB" sz="1400" baseline="0"/>
@@ -2340,7 +2339,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-GB"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2775,7 +2774,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-GB"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -2897,7 +2896,7 @@
                   <a:cs typeface="+mn-cs"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="en-GB"/>
             </a:p>
           </c:txPr>
         </c:title>
@@ -5373,35 +5372,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69DD871A-B658-3E4D-9134-2FA508086801}" name="Table1" displayName="Table1" ref="A1:I701" totalsRowShown="0" dataDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{69DD871A-B658-3E4D-9134-2FA508086801}" name="Table1" displayName="Table1" ref="A1:I701" totalsRowShown="0" dataDxfId="15">
   <autoFilter ref="A1:I701" xr:uid="{69DD871A-B658-3E4D-9134-2FA508086801}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{3C9287AD-66E2-F34F-91EA-80AECC4FCFA7}" name="n" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{CE727602-53C2-E641-A5EF-387CB278CE12}" name="Nx" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{CC454B36-B116-9747-BBC9-E0AD7087CC3A}" name="Ny" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{65FC7912-7741-ED4E-BC70-2E1E02A5B980}" name="step" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{52DA33B3-8CC2-AF42-9DF9-FDCA4CB156D6}" name="mat_time" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{82CD9D3E-EABE-8C41-8D68-C4906A95CB10}" name="tn_time" dataDxfId="14"/>
-    <tableColumn id="9" xr3:uid="{6EC4DE00-FCF5-4A4A-9CF9-1C84490B04B7}" name="mat_build" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{6FB119F4-70DE-414B-B4AD-4908BB53E3B3}" name="mps_build" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{712E6D29-748F-C844-90DE-6FE192B73F81}" name="mpo_build" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{3C9287AD-66E2-F34F-91EA-80AECC4FCFA7}" name="n" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{CE727602-53C2-E641-A5EF-387CB278CE12}" name="Nx" dataDxfId="13"/>
+    <tableColumn id="3" xr3:uid="{CC454B36-B116-9747-BBC9-E0AD7087CC3A}" name="Ny" dataDxfId="12"/>
+    <tableColumn id="4" xr3:uid="{65FC7912-7741-ED4E-BC70-2E1E02A5B980}" name="step" dataDxfId="11"/>
+    <tableColumn id="5" xr3:uid="{52DA33B3-8CC2-AF42-9DF9-FDCA4CB156D6}" name="mat_time" dataDxfId="10"/>
+    <tableColumn id="6" xr3:uid="{82CD9D3E-EABE-8C41-8D68-C4906A95CB10}" name="tn_time" dataDxfId="9"/>
+    <tableColumn id="9" xr3:uid="{6EC4DE00-FCF5-4A4A-9CF9-1C84490B04B7}" name="mat_build" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{6FB119F4-70DE-414B-B4AD-4908BB53E3B3}" name="mps_build" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{712E6D29-748F-C844-90DE-6FE192B73F81}" name="mpo_build" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{52CC4271-737A-7743-9E9C-14F013317013}" name="Table2" displayName="Table2" ref="A1:D8" totalsRowShown="0" dataDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{52CC4271-737A-7743-9E9C-14F013317013}" name="Table2" displayName="Table2" ref="A1:D8" totalsRowShown="0" dataDxfId="20">
   <autoFilter ref="A1:D8" xr:uid="{52CC4271-737A-7743-9E9C-14F013317013}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{1318D5EC-682A-7D4A-8D44-E27AA37130DB}" name="n" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{1E076BEF-2430-0F4B-AE76-62F7135F06FE}" name="N=2^n" dataDxfId="0">
+    <tableColumn id="1" xr3:uid="{1318D5EC-682A-7D4A-8D44-E27AA37130DB}" name="n" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{1E076BEF-2430-0F4B-AE76-62F7135F06FE}" name="N=2^n" dataDxfId="18">
       <calculatedColumnFormula>2^Table2[[#This Row],[n]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{3E32F3CF-8916-0D4B-9C49-A9ADB0FDAA5A}" name="Matrix" dataDxfId="3">
+    <tableColumn id="2" xr3:uid="{3E32F3CF-8916-0D4B-9C49-A9ADB0FDAA5A}" name="Matrix" dataDxfId="17">
       <calculatedColumnFormula array="1">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!E:E,matrix_vs_tn_time!A:A=A2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{DC66C0E1-8197-4240-B8D2-8C9AF1BB27B9}" name="TN" dataDxfId="2">
+    <tableColumn id="3" xr3:uid="{DC66C0E1-8197-4240-B8D2-8C9AF1BB27B9}" name="TN" dataDxfId="16">
       <calculatedColumnFormula array="1">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!F:F,matrix_vs_tn_time!A:A=A2))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -5413,20 +5412,20 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{D8044509-3D7D-D249-8217-3739FE4A9328}" name="Table3" displayName="Table3" ref="A1:F8" totalsRowShown="0">
   <autoFilter ref="A1:F8" xr:uid="{D8044509-3D7D-D249-8217-3739FE4A9328}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{D003EBCA-3296-B744-B5B8-24A5CF1BCC80}" name="n" dataDxfId="10"/>
-    <tableColumn id="6" xr3:uid="{E07C5AF6-F3C0-134F-8924-61C73768B704}" name="N=2^n" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{D003EBCA-3296-B744-B5B8-24A5CF1BCC80}" name="n" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{E07C5AF6-F3C0-134F-8924-61C73768B704}" name="N=2^n" dataDxfId="4">
       <calculatedColumnFormula>2^Table3[[#This Row],[n]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{7E457332-497D-5447-A666-D15F61ADB2AC}" name="MPS (s)" dataDxfId="9">
+    <tableColumn id="3" xr3:uid="{7E457332-497D-5447-A666-D15F61ADB2AC}" name="MPS (s)" dataDxfId="3">
       <calculatedColumnFormula array="1">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!H:H,matrix_vs_tn_time!$A:$A=$A2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{93172FA6-1349-FF44-B468-C54018D217DB}" name="MPO (s)" dataDxfId="7">
+    <tableColumn id="4" xr3:uid="{93172FA6-1349-FF44-B468-C54018D217DB}" name="MPO (s)" dataDxfId="2">
       <calculatedColumnFormula array="1">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!I:I,matrix_vs_tn_time!$A:$A=$A2))</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{B3EB527A-A2E4-764C-B840-E0422239DA5F}" name="TN=MPS+MPO (s)" dataDxfId="8">
+    <tableColumn id="5" xr3:uid="{B3EB527A-A2E4-764C-B840-E0422239DA5F}" name="TN=MPS+MPO (s)" dataDxfId="1">
       <calculatedColumnFormula>C2+D2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{957F1B12-B2CF-7342-B5E1-3676122282E0}" name="Matrix (s)" dataDxfId="6">
+    <tableColumn id="2" xr3:uid="{957F1B12-B2CF-7342-B5E1-3676122282E0}" name="Matrix (s)" dataDxfId="0">
       <calculatedColumnFormula array="1">MEDIAN(_xlfn._xlws.FILTER(matrix_vs_tn_time!G:G,matrix_vs_tn_time!$A:$A=$A2))</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -26408,7 +26407,7 @@
       <c r="A8" s="6">
         <v>10</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B8" s="5">
         <f>2^Table3[[#This Row],[n]]</f>
         <v>1024</v>
       </c>
